--- a/2022 data/excel_outputs/170_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/170_boothwise_data.xlsx
@@ -14,11 +14,89 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="663">
   <si>
     <t>AC 170 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -67,7 +145,7 @@
     <t>praa0vi0 revrii</t>
   </si>
   <si>
-    <t>####0##0 ###### ########</t>
+    <t>NAN</t>
   </si>
   <si>
     <t>praa0vi0 ghlvaaraa</t>
@@ -1931,8 +2009,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1948,7 +2034,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1956,12 +2042,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2260,91 +2364,169 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>612</v>
+        <v>638</v>
       </c>
       <c r="D2" t="s">
-        <v>613</v>
+        <v>639</v>
       </c>
       <c r="E2" t="s">
-        <v>614</v>
+        <v>640</v>
       </c>
       <c r="F2" t="s">
-        <v>615</v>
+        <v>641</v>
       </c>
       <c r="G2" t="s">
-        <v>616</v>
+        <v>642</v>
       </c>
       <c r="H2" t="s">
-        <v>617</v>
+        <v>643</v>
       </c>
       <c r="I2" t="s">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="J2" t="s">
-        <v>619</v>
+        <v>645</v>
       </c>
       <c r="K2" t="s">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="L2" t="s">
-        <v>621</v>
+        <v>647</v>
       </c>
       <c r="M2" t="s">
-        <v>622</v>
+        <v>648</v>
       </c>
       <c r="N2" t="s">
-        <v>623</v>
+        <v>649</v>
       </c>
       <c r="O2" t="s">
-        <v>624</v>
+        <v>650</v>
       </c>
       <c r="P2" t="s">
-        <v>625</v>
+        <v>651</v>
       </c>
       <c r="Q2" t="s">
-        <v>626</v>
+        <v>652</v>
       </c>
       <c r="R2" t="s">
-        <v>627</v>
+        <v>653</v>
       </c>
       <c r="S2" t="s">
-        <v>628</v>
+        <v>654</v>
       </c>
       <c r="T2" t="s">
-        <v>629</v>
+        <v>655</v>
       </c>
       <c r="U2" t="s">
-        <v>630</v>
+        <v>656</v>
       </c>
       <c r="V2" t="s">
-        <v>631</v>
+        <v>657</v>
       </c>
       <c r="W2" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="X2" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="Y2" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="Z2" t="s">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="AA2" t="s">
-        <v>636</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -2352,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>1151</v>
@@ -2435,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>1053</v>
@@ -2518,7 +2700,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C5">
         <v>914</v>
@@ -2601,7 +2783,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C6">
         <v>983</v>
@@ -2684,7 +2866,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7">
         <v>813</v>
@@ -2767,7 +2949,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>671</v>
@@ -2850,7 +3032,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>654</v>
@@ -2933,7 +3115,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C10">
         <v>775</v>
@@ -3016,7 +3198,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>520</v>
@@ -3099,7 +3281,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C12">
         <v>1115</v>
@@ -3182,7 +3364,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>615</v>
@@ -3265,7 +3447,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C14">
         <v>596</v>
@@ -3348,7 +3530,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>1110</v>
@@ -3431,7 +3613,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>638</v>
@@ -3514,7 +3696,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>407</v>
@@ -3597,7 +3779,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>703</v>
@@ -3680,7 +3862,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>729</v>
@@ -3763,7 +3945,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C20">
         <v>902</v>
@@ -3846,7 +4028,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C21">
         <v>386</v>
@@ -3929,7 +4111,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>653</v>
@@ -4012,7 +4194,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C23">
         <v>648</v>
@@ -4095,7 +4277,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C24">
         <v>996</v>
@@ -4178,7 +4360,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C25">
         <v>1013</v>
@@ -4261,7 +4443,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C26">
         <v>917</v>
@@ -4344,7 +4526,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C27">
         <v>455</v>
@@ -4427,7 +4609,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>1021</v>
@@ -4510,7 +4692,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C29">
         <v>919</v>
@@ -4593,7 +4775,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C30">
         <v>579</v>
@@ -4676,7 +4858,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="C31">
         <v>645</v>
@@ -4759,7 +4941,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>686</v>
@@ -4842,7 +5024,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>745</v>
@@ -4925,7 +5107,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>1075</v>
@@ -5008,7 +5190,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="C35">
         <v>997</v>
@@ -5091,7 +5273,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="C36">
         <v>740</v>
@@ -5174,7 +5356,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C37">
         <v>743</v>
@@ -5257,7 +5439,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="C38">
         <v>683</v>
@@ -5340,7 +5522,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="C39">
         <v>475</v>
@@ -5423,7 +5605,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C40">
         <v>867</v>
@@ -5506,7 +5688,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>765</v>
@@ -5589,7 +5771,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C42">
         <v>820</v>
@@ -5672,7 +5854,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>844</v>
@@ -5755,7 +5937,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C44">
         <v>947</v>
@@ -5838,7 +6020,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C45">
         <v>1153</v>
@@ -5921,7 +6103,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C46">
         <v>983</v>
@@ -6004,7 +6186,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>1108</v>
@@ -6087,7 +6269,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C48">
         <v>473</v>
@@ -6170,7 +6352,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C49">
         <v>767</v>
@@ -6253,7 +6435,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C50">
         <v>977</v>
@@ -6336,7 +6518,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C51">
         <v>1031</v>
@@ -6419,7 +6601,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C52">
         <v>1025</v>
@@ -6502,7 +6684,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C53">
         <v>863</v>
@@ -6585,7 +6767,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C54">
         <v>1089</v>
@@ -6668,7 +6850,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C55">
         <v>1058</v>
@@ -6751,7 +6933,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>829</v>
@@ -6834,7 +7016,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C57">
         <v>737</v>
@@ -6917,7 +7099,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C58">
         <v>708</v>
@@ -7000,7 +7182,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C59">
         <v>958</v>
@@ -7083,7 +7265,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>922</v>
@@ -7166,7 +7348,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>960</v>
@@ -7249,7 +7431,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>909</v>
@@ -7332,7 +7514,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C63">
         <v>869</v>
@@ -7415,7 +7597,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C64">
         <v>930</v>
@@ -7498,7 +7680,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C65">
         <v>814</v>
@@ -7581,7 +7763,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C66">
         <v>392</v>
@@ -7664,7 +7846,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C67">
         <v>661</v>
@@ -7747,7 +7929,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>630</v>
@@ -7830,7 +8012,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>1037</v>
@@ -7913,7 +8095,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>1003</v>
@@ -7996,7 +8178,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>976</v>
@@ -8079,7 +8261,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>734</v>
@@ -8162,7 +8344,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>390</v>
@@ -8245,7 +8427,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C74">
         <v>1193</v>
@@ -8328,7 +8510,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C75">
         <v>703</v>
@@ -8411,7 +8593,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="C76">
         <v>1020</v>
@@ -8494,7 +8676,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C77">
         <v>946</v>
@@ -8577,7 +8759,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C78">
         <v>624</v>
@@ -8660,7 +8842,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C79">
         <v>928</v>
@@ -8743,7 +8925,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="C80">
         <v>700</v>
@@ -8826,7 +9008,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C81">
         <v>855</v>
@@ -8909,7 +9091,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="C82">
         <v>521</v>
@@ -8992,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="C83">
         <v>1114</v>
@@ -9075,7 +9257,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="C84">
         <v>1063</v>
@@ -9158,7 +9340,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="C85">
         <v>1159</v>
@@ -9241,7 +9423,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="C86">
         <v>976</v>
@@ -9324,7 +9506,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C87">
         <v>1057</v>
@@ -9407,7 +9589,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="C88">
         <v>747</v>
@@ -9490,7 +9672,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C89">
         <v>959</v>
@@ -9573,7 +9755,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="C90">
         <v>1005</v>
@@ -9656,7 +9838,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C91">
         <v>1087</v>
@@ -9739,7 +9921,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C92">
         <v>1019</v>
@@ -9822,7 +10004,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="C93">
         <v>1031</v>
@@ -9905,7 +10087,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="C94">
         <v>1041</v>
@@ -9988,7 +10170,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="C95">
         <v>1057</v>
@@ -10071,7 +10253,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C96">
         <v>1049</v>
@@ -10154,7 +10336,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="C97">
         <v>1144</v>
@@ -10237,7 +10419,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C98">
         <v>992</v>
@@ -10320,7 +10502,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C99">
         <v>677</v>
@@ -10403,7 +10585,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C100">
         <v>801</v>
@@ -10486,7 +10668,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C101">
         <v>775</v>
@@ -10569,7 +10751,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C102">
         <v>702</v>
@@ -10652,7 +10834,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C103">
         <v>1159</v>
@@ -10735,7 +10917,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C104">
         <v>890</v>
@@ -10818,7 +11000,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C105">
         <v>1040</v>
@@ -10901,7 +11083,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C106">
         <v>1008</v>
@@ -10984,7 +11166,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C107">
         <v>925</v>
@@ -11067,7 +11249,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C108">
         <v>1112</v>
@@ -11150,7 +11332,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C109">
         <v>1057</v>
@@ -11233,7 +11415,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C110">
         <v>1024</v>
@@ -11316,7 +11498,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C111">
         <v>910</v>
@@ -11399,7 +11581,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C112">
         <v>1012</v>
@@ -11482,7 +11664,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C113">
         <v>1012</v>
@@ -11565,7 +11747,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="C114">
         <v>1020</v>
@@ -11648,7 +11830,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="C115">
         <v>896</v>
@@ -11731,7 +11913,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="C116">
         <v>1061</v>
@@ -11814,7 +11996,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="C117">
         <v>1023</v>
@@ -11897,7 +12079,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C118">
         <v>910</v>
@@ -11980,7 +12162,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="C119">
         <v>1125</v>
@@ -12063,7 +12245,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C120">
         <v>910</v>
@@ -12146,7 +12328,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C121">
         <v>1087</v>
@@ -12229,7 +12411,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C122">
         <v>1007</v>
@@ -12312,7 +12494,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C123">
         <v>850</v>
@@ -12395,7 +12577,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C124">
         <v>1111</v>
@@ -12478,7 +12660,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="C125">
         <v>775</v>
@@ -12561,7 +12743,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C126">
         <v>973</v>
@@ -12644,7 +12826,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="C127">
         <v>934</v>
@@ -12727,7 +12909,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="C128">
         <v>1177</v>
@@ -12810,7 +12992,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C129">
         <v>1037</v>
@@ -12893,7 +13075,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="C130">
         <v>997</v>
@@ -12976,7 +13158,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="C131">
         <v>913</v>
@@ -13059,7 +13241,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="C132">
         <v>1077</v>
@@ -13142,7 +13324,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="C133">
         <v>797</v>
@@ -13225,7 +13407,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C134">
         <v>1031</v>
@@ -13308,7 +13490,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="C135">
         <v>1017</v>
@@ -13391,7 +13573,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="C136">
         <v>995</v>
@@ -13474,7 +13656,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="C137">
         <v>873</v>
@@ -13557,7 +13739,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="C138">
         <v>786</v>
@@ -13640,7 +13822,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="C139">
         <v>1151</v>
@@ -13723,7 +13905,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="C140">
         <v>982</v>
@@ -13806,7 +13988,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="C141">
         <v>889</v>
@@ -13889,7 +14071,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="C142">
         <v>933</v>
@@ -13972,7 +14154,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="C143">
         <v>1046</v>
@@ -14055,7 +14237,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="C144">
         <v>964</v>
@@ -14138,7 +14320,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="C145">
         <v>1032</v>
@@ -14221,7 +14403,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="C146">
         <v>634</v>
@@ -14304,7 +14486,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C147">
         <v>706</v>
@@ -14387,7 +14569,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C148">
         <v>739</v>
@@ -14470,7 +14652,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C149">
         <v>1044</v>
@@ -14553,7 +14735,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="C150">
         <v>875</v>
@@ -14636,7 +14818,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="C151">
         <v>1105</v>
@@ -14719,7 +14901,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="C152">
         <v>1013</v>
@@ -14802,7 +14984,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="C153">
         <v>477</v>
@@ -14885,7 +15067,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C154">
         <v>801</v>
@@ -14968,7 +15150,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="C155">
         <v>1125</v>
@@ -15051,7 +15233,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C156">
         <v>814</v>
@@ -15134,7 +15316,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="C157">
         <v>837</v>
@@ -15217,7 +15399,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
       <c r="C158">
         <v>1053</v>
@@ -15300,7 +15482,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="C159">
         <v>1025</v>
@@ -15383,7 +15565,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C160">
         <v>1006</v>
@@ -15466,7 +15648,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C161">
         <v>1021</v>
@@ -15549,7 +15731,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="C162">
         <v>1151</v>
@@ -15632,7 +15814,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="C163">
         <v>996</v>
@@ -15715,7 +15897,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="C164">
         <v>1200</v>
@@ -15798,7 +15980,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C165">
         <v>997</v>
@@ -15881,7 +16063,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="C166">
         <v>1021</v>
@@ -15964,7 +16146,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="C167">
         <v>925</v>
@@ -16047,7 +16229,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
       <c r="C168">
         <v>941</v>
@@ -16130,7 +16312,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="C169">
         <v>1143</v>
@@ -16213,7 +16395,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="C170">
         <v>1172</v>
@@ -16296,7 +16478,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C171">
         <v>844</v>
@@ -16379,7 +16561,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="C172">
         <v>906</v>
@@ -16462,7 +16644,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="C173">
         <v>906</v>
@@ -16545,7 +16727,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="C174">
         <v>1049</v>
@@ -16628,7 +16810,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="C175">
         <v>749</v>
@@ -16711,7 +16893,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C176">
         <v>1054</v>
@@ -16794,7 +16976,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="C177">
         <v>890</v>
@@ -16877,7 +17059,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C178">
         <v>766</v>
@@ -16960,7 +17142,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="C179">
         <v>824</v>
@@ -17043,7 +17225,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C180">
         <v>993</v>
@@ -17126,7 +17308,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="C181">
         <v>955</v>
@@ -17209,7 +17391,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="C182">
         <v>759</v>
@@ -17292,7 +17474,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C183">
         <v>1026</v>
@@ -17375,7 +17557,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>210</v>
       </c>
       <c r="C184">
         <v>904</v>
@@ -17458,7 +17640,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="C185">
         <v>984</v>
@@ -17541,7 +17723,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>212</v>
       </c>
       <c r="C186">
         <v>1050</v>
@@ -17624,7 +17806,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="C187">
         <v>952</v>
@@ -17707,7 +17889,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C188">
         <v>1069</v>
@@ -17790,7 +17972,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C189">
         <v>1051</v>
@@ -17873,7 +18055,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="C190">
         <v>1044</v>
@@ -17956,7 +18138,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="C191">
         <v>692</v>
@@ -18039,7 +18221,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="C192">
         <v>687</v>
@@ -18122,7 +18304,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="C193">
         <v>1054</v>
@@ -18205,7 +18387,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C194">
         <v>1007</v>
@@ -18288,7 +18470,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C195">
         <v>1060</v>
@@ -18371,7 +18553,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C196">
         <v>1048</v>
@@ -18454,7 +18636,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C197">
         <v>847</v>
@@ -18537,7 +18719,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="C198">
         <v>1020</v>
@@ -18620,7 +18802,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="C199">
         <v>737</v>
@@ -18703,7 +18885,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C200">
         <v>665</v>
@@ -18786,7 +18968,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="C201">
         <v>1079</v>
@@ -18869,7 +19051,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="C202">
         <v>1069</v>
@@ -18952,7 +19134,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="C203">
         <v>894</v>
@@ -19035,7 +19217,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="C204">
         <v>952</v>
@@ -19118,7 +19300,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="C205">
         <v>1069</v>
@@ -19201,7 +19383,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="C206">
         <v>628</v>
@@ -19284,7 +19466,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="C207">
         <v>984</v>
@@ -19367,7 +19549,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="C208">
         <v>993</v>
@@ -19450,7 +19632,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C209">
         <v>906</v>
@@ -19533,7 +19715,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="C210">
         <v>1062</v>
@@ -19616,7 +19798,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>237</v>
       </c>
       <c r="C211">
         <v>910</v>
@@ -19699,7 +19881,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="C212">
         <v>639</v>
@@ -19782,7 +19964,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="C213">
         <v>1182</v>
@@ -19865,7 +20047,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="C214">
         <v>913</v>
@@ -19948,7 +20130,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
       <c r="C215">
         <v>893</v>
@@ -20031,7 +20213,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C216">
         <v>735</v>
@@ -20114,7 +20296,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C217">
         <v>971</v>
@@ -20197,7 +20379,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="C218">
         <v>873</v>
@@ -20280,7 +20462,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="C219">
         <v>674</v>
@@ -20363,7 +20545,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="C220">
         <v>942</v>
@@ -20446,7 +20628,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C221">
         <v>982</v>
@@ -20529,7 +20711,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="C222">
         <v>945</v>
@@ -20612,7 +20794,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>249</v>
       </c>
       <c r="C223">
         <v>949</v>
@@ -20695,7 +20877,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>250</v>
       </c>
       <c r="C224">
         <v>959</v>
@@ -20778,7 +20960,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C225">
         <v>1120</v>
@@ -20861,7 +21043,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="C226">
         <v>820</v>
@@ -20944,7 +21126,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="C227">
         <v>963</v>
@@ -21027,7 +21209,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="C228">
         <v>979</v>
@@ -21110,7 +21292,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="C229">
         <v>1134</v>
@@ -21193,7 +21375,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="C230">
         <v>942</v>
@@ -21276,7 +21458,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>257</v>
       </c>
       <c r="C231">
         <v>1000</v>
@@ -21359,7 +21541,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C232">
         <v>863</v>
@@ -21442,7 +21624,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="C233">
         <v>858</v>
@@ -21525,7 +21707,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="C234">
         <v>883</v>
@@ -21608,7 +21790,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="C235">
         <v>912</v>
@@ -21691,7 +21873,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>262</v>
       </c>
       <c r="C236">
         <v>859</v>
@@ -21774,7 +21956,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="C237">
         <v>973</v>
@@ -21857,7 +22039,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="C238">
         <v>1202</v>
@@ -21940,7 +22122,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="C239">
         <v>992</v>
@@ -22023,7 +22205,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="C240">
         <v>978</v>
@@ -22106,7 +22288,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="C241">
         <v>1020</v>
@@ -22189,7 +22371,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>268</v>
       </c>
       <c r="C242">
         <v>987</v>
@@ -22272,7 +22454,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="C243">
         <v>1071</v>
@@ -22355,7 +22537,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C244">
         <v>987</v>
@@ -22438,7 +22620,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C245">
         <v>839</v>
@@ -22521,7 +22703,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>272</v>
       </c>
       <c r="C246">
         <v>959</v>
@@ -22604,7 +22786,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>273</v>
       </c>
       <c r="C247">
         <v>468</v>
@@ -22687,7 +22869,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="C248">
         <v>789</v>
@@ -22770,7 +22952,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="C249">
         <v>709</v>
@@ -22853,7 +23035,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="C250">
         <v>970</v>
@@ -22936,7 +23118,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="C251">
         <v>1028</v>
@@ -23019,7 +23201,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="C252">
         <v>748</v>
@@ -23102,7 +23284,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>279</v>
       </c>
       <c r="C253">
         <v>809</v>
@@ -23185,7 +23367,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="C254">
         <v>933</v>
@@ -23268,7 +23450,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C255">
         <v>1038</v>
@@ -23351,7 +23533,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="C256">
         <v>930</v>
@@ -23434,7 +23616,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="C257">
         <v>953</v>
@@ -23517,7 +23699,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="C258">
         <v>602</v>
@@ -23600,7 +23782,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="C259">
         <v>592</v>
@@ -23683,7 +23865,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="C260">
         <v>429</v>
@@ -23766,7 +23948,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="C261">
         <v>756</v>
@@ -23849,7 +24031,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="C262">
         <v>623</v>
@@ -23932,7 +24114,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="C263">
         <v>577</v>
@@ -24015,7 +24197,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C264">
         <v>1019</v>
@@ -24098,7 +24280,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C265">
         <v>1020</v>
@@ -24181,7 +24363,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="C266">
         <v>592</v>
@@ -24264,7 +24446,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="C267">
         <v>539</v>
@@ -24347,7 +24529,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="C268">
         <v>886</v>
@@ -24430,7 +24612,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>295</v>
       </c>
       <c r="C269">
         <v>1115</v>
@@ -24513,7 +24695,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>296</v>
       </c>
       <c r="C270">
         <v>873</v>
@@ -24596,7 +24778,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="C271">
         <v>887</v>
@@ -24679,7 +24861,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="C272">
         <v>799</v>
@@ -24762,7 +24944,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="C273">
         <v>1037</v>
@@ -24845,7 +25027,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="C274">
         <v>679</v>
@@ -24928,7 +25110,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="C275">
         <v>1049</v>
@@ -25011,7 +25193,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>302</v>
       </c>
       <c r="C276">
         <v>999</v>
@@ -25094,7 +25276,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>303</v>
       </c>
       <c r="C277">
         <v>697</v>
@@ -25177,7 +25359,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>304</v>
       </c>
       <c r="C278">
         <v>704</v>
@@ -25260,7 +25442,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="C279">
         <v>487</v>
@@ -25343,7 +25525,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="C280">
         <v>637</v>
@@ -25426,7 +25608,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="C281">
         <v>522</v>
@@ -25509,7 +25691,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>308</v>
       </c>
       <c r="C282">
         <v>665</v>
@@ -25592,7 +25774,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>309</v>
       </c>
       <c r="C283">
         <v>740</v>
@@ -25675,7 +25857,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
       <c r="C284">
         <v>725</v>
@@ -25758,7 +25940,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>311</v>
       </c>
       <c r="C285">
         <v>1052</v>
@@ -25841,7 +26023,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="C286">
         <v>732</v>
@@ -25924,7 +26106,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="C287">
         <v>883</v>
@@ -26007,7 +26189,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="C288">
         <v>1125</v>
@@ -26090,7 +26272,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="C289">
         <v>639</v>
@@ -26173,7 +26355,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="C290">
         <v>638</v>
@@ -26256,7 +26438,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="C291">
         <v>1142</v>
@@ -26339,7 +26521,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="C292">
         <v>802</v>
@@ -26422,7 +26604,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="C293">
         <v>722</v>
@@ -26505,7 +26687,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="C294">
         <v>484</v>
@@ -26588,7 +26770,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>321</v>
       </c>
       <c r="C295">
         <v>428</v>
@@ -26671,7 +26853,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="C296">
         <v>924</v>
@@ -26754,7 +26936,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="C297">
         <v>939</v>
@@ -26837,7 +27019,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="C298">
         <v>586</v>
@@ -26920,7 +27102,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="C299">
         <v>622</v>
@@ -27003,7 +27185,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="C300">
         <v>1080</v>
@@ -27086,7 +27268,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="C301">
         <v>414</v>
@@ -27169,7 +27351,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="C302">
         <v>673</v>
@@ -27252,7 +27434,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>329</v>
       </c>
       <c r="C303">
         <v>593</v>
@@ -27335,7 +27517,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="C304">
         <v>864</v>
@@ -27418,7 +27600,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>331</v>
       </c>
       <c r="C305">
         <v>804</v>
@@ -27501,7 +27683,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="C306">
         <v>799</v>
@@ -27584,7 +27766,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="C307">
         <v>1108</v>
@@ -27667,7 +27849,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>334</v>
       </c>
       <c r="C308">
         <v>853</v>
@@ -27750,7 +27932,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="C309">
         <v>846</v>
@@ -27833,7 +28015,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="C310">
         <v>734</v>
@@ -27916,7 +28098,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>337</v>
       </c>
       <c r="C311">
         <v>856</v>
@@ -27999,7 +28181,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="C312">
         <v>667</v>
@@ -28082,7 +28264,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>339</v>
       </c>
       <c r="C313">
         <v>955</v>
@@ -28165,7 +28347,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C314">
         <v>1131</v>
@@ -28248,7 +28430,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="C315">
         <v>764</v>
@@ -28331,7 +28513,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="C316">
         <v>744</v>
@@ -28414,7 +28596,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="C317">
         <v>675</v>
@@ -28497,7 +28679,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="C318">
         <v>667</v>
@@ -28580,7 +28762,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="C319">
         <v>401</v>
@@ -28663,7 +28845,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="C320">
         <v>927</v>
@@ -28746,7 +28928,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="C321">
         <v>984</v>
@@ -28829,7 +29011,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="C322">
         <v>1096</v>
@@ -28912,7 +29094,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="C323">
         <v>1095</v>
@@ -28995,7 +29177,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="C324">
         <v>937</v>
@@ -29078,7 +29260,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="C325">
         <v>1140</v>
@@ -29161,7 +29343,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="C326">
         <v>764</v>
@@ -29244,7 +29426,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="C327">
         <v>799</v>
@@ -29327,7 +29509,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="C328">
         <v>1052</v>
@@ -29410,7 +29592,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="C329">
         <v>939</v>
@@ -29493,7 +29675,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="C330">
         <v>572</v>
@@ -29576,7 +29758,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C331">
         <v>1008</v>
@@ -29659,7 +29841,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="C332">
         <v>1099</v>
@@ -29742,7 +29924,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C333">
         <v>347</v>
@@ -29825,7 +30007,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="C334">
         <v>643</v>
@@ -29908,7 +30090,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="C335">
         <v>649</v>
@@ -29991,7 +30173,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="C336">
         <v>578</v>
@@ -30074,7 +30256,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="C337">
         <v>978</v>
@@ -30157,7 +30339,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="C338">
         <v>589</v>
@@ -30240,7 +30422,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="C339">
         <v>713</v>
@@ -30323,7 +30505,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="C340">
         <v>1173</v>
@@ -30406,7 +30588,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="C341">
         <v>946</v>
@@ -30489,7 +30671,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="C342">
         <v>1123</v>
@@ -30572,7 +30754,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C343">
         <v>1076</v>
@@ -30655,7 +30837,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C344">
         <v>1113</v>
@@ -30738,7 +30920,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="C345">
         <v>1039</v>
@@ -30821,7 +31003,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="C346">
         <v>631</v>
@@ -30904,7 +31086,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="C347">
         <v>1086</v>
@@ -30987,7 +31169,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="C348">
         <v>1184</v>
@@ -31070,7 +31252,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C349">
         <v>842</v>
@@ -31153,7 +31335,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="C350">
         <v>927</v>
@@ -31236,7 +31418,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C351">
         <v>512</v>
@@ -31319,7 +31501,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="C352">
         <v>990</v>
@@ -31402,7 +31584,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="C353">
         <v>1148</v>
@@ -31485,7 +31667,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="C354">
         <v>1010</v>
@@ -31568,7 +31750,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="C355">
         <v>1021</v>
@@ -31651,7 +31833,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="C356">
         <v>936</v>
@@ -31734,7 +31916,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="C357">
         <v>987</v>
@@ -31817,7 +31999,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="C358">
         <v>978</v>
@@ -31900,7 +32082,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="C359">
         <v>1052</v>
@@ -31983,7 +32165,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C360">
         <v>1080</v>
@@ -32066,7 +32248,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="C361">
         <v>1081</v>
@@ -32149,7 +32331,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="C362">
         <v>861</v>
@@ -32232,7 +32414,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C363">
         <v>940</v>
@@ -32315,7 +32497,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="C364">
         <v>1043</v>
@@ -32398,7 +32580,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="C365">
         <v>917</v>
@@ -32481,7 +32663,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="C366">
         <v>1020</v>
@@ -32564,7 +32746,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="C367">
         <v>1103</v>
@@ -32647,7 +32829,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="C368">
         <v>678</v>
@@ -32730,7 +32912,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="C369">
         <v>993</v>
@@ -32813,7 +32995,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="C370">
         <v>1147</v>
@@ -32896,7 +33078,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="C371">
         <v>1016</v>
@@ -32979,7 +33161,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="C372">
         <v>1112</v>
@@ -33062,7 +33244,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="C373">
         <v>913</v>
@@ -33145,7 +33327,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="C374">
         <v>790</v>
@@ -33228,7 +33410,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="C375">
         <v>1143</v>
@@ -33311,7 +33493,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="C376">
         <v>1089</v>
@@ -33394,7 +33576,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="C377">
         <v>1155</v>
@@ -33477,7 +33659,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="C378">
         <v>984</v>
@@ -33560,7 +33742,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="C379">
         <v>907</v>
@@ -33643,7 +33825,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="C380">
         <v>1043</v>
@@ -33726,7 +33908,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="C381">
         <v>1072</v>
@@ -33809,7 +33991,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="C382">
         <v>1053</v>
@@ -33892,7 +34074,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="C383">
         <v>988</v>
@@ -33975,7 +34157,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="C384">
         <v>995</v>
@@ -34058,7 +34240,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="C385">
         <v>1024</v>
@@ -34141,7 +34323,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="C386">
         <v>948</v>
@@ -34224,7 +34406,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="C387">
         <v>786</v>
@@ -34307,7 +34489,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="C388">
         <v>1213</v>
@@ -34390,7 +34572,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="C389">
         <v>1138</v>
@@ -34473,7 +34655,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="C390">
         <v>1049</v>
@@ -34556,7 +34738,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="C391">
         <v>827</v>
@@ -34639,7 +34821,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="C392">
         <v>795</v>
@@ -34722,7 +34904,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="C393">
         <v>1156</v>
@@ -34805,7 +34987,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="C394">
         <v>1180</v>
@@ -34888,7 +35070,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="C395">
         <v>1134</v>
@@ -34971,7 +35153,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C396">
         <v>949</v>
@@ -35054,7 +35236,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="C397">
         <v>946</v>
@@ -35137,7 +35319,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="C398">
         <v>914</v>
@@ -35220,7 +35402,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="C399">
         <v>1051</v>
@@ -35303,7 +35485,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="C400">
         <v>936</v>
@@ -35386,7 +35568,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="C401">
         <v>861</v>
@@ -35469,7 +35651,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="C402">
         <v>1132</v>
@@ -35552,7 +35734,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="C403">
         <v>1043</v>
@@ -35635,7 +35817,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="C404">
         <v>1018</v>
@@ -35718,7 +35900,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="C405">
         <v>1073</v>
@@ -35801,7 +35983,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="C406">
         <v>1136</v>
@@ -35884,7 +36066,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="C407">
         <v>1123</v>
@@ -35967,7 +36149,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="C408">
         <v>1095</v>
@@ -36050,7 +36232,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="C409">
         <v>1104</v>
@@ -36133,7 +36315,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="C410">
         <v>1077</v>
@@ -36216,7 +36398,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="C411">
         <v>1175</v>
@@ -36299,7 +36481,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="C412">
         <v>1170</v>
@@ -36382,7 +36564,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="C413">
         <v>1169</v>
@@ -36465,7 +36647,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="C414">
         <v>1037</v>
@@ -36548,7 +36730,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="C415">
         <v>1023</v>
@@ -36631,7 +36813,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="C416">
         <v>930</v>
@@ -36714,7 +36896,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="C417">
         <v>924</v>
@@ -36797,7 +36979,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="C418">
         <v>1029</v>
@@ -36880,7 +37062,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="C419">
         <v>868</v>
@@ -36963,7 +37145,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="C420">
         <v>1028</v>
@@ -37046,7 +37228,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="C421">
         <v>1059</v>
@@ -37129,7 +37311,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="C422">
         <v>1117</v>
@@ -37212,7 +37394,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C423">
         <v>1096</v>
@@ -37295,7 +37477,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="C424">
         <v>1130</v>
@@ -37378,7 +37560,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="C425">
         <v>959</v>
@@ -37461,7 +37643,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="C426">
         <v>1031</v>
@@ -37544,7 +37726,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="C427">
         <v>941</v>
@@ -37627,7 +37809,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="C428">
         <v>971</v>
@@ -37710,7 +37892,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="C429">
         <v>838</v>
@@ -37793,7 +37975,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="C430">
         <v>493</v>
@@ -37876,7 +38058,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="C431">
         <v>1081</v>
@@ -37959,7 +38141,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="C432">
         <v>905</v>
@@ -38042,7 +38224,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="C433">
         <v>777</v>
@@ -38125,7 +38307,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="C434">
         <v>689</v>
@@ -38208,7 +38390,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="C435">
         <v>1109</v>
@@ -38291,7 +38473,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="C436">
         <v>1087</v>
@@ -38374,7 +38556,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="C437">
         <v>1073</v>
@@ -38457,7 +38639,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="C438">
         <v>1162</v>
@@ -38540,7 +38722,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="C439">
         <v>1164</v>
@@ -38623,7 +38805,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="C440">
         <v>826</v>
@@ -38706,7 +38888,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="C441">
         <v>992</v>
@@ -38789,7 +38971,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="C442">
         <v>828</v>
@@ -38872,7 +39054,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="C443">
         <v>1015</v>
@@ -38955,7 +39137,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="C444">
         <v>1054</v>
@@ -39038,7 +39220,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="C445">
         <v>1013</v>
@@ -39121,7 +39303,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>446</v>
+        <v>472</v>
       </c>
       <c r="C446">
         <v>1237</v>
@@ -39204,7 +39386,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>447</v>
+        <v>473</v>
       </c>
       <c r="C447">
         <v>1078</v>
@@ -39287,7 +39469,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="C448">
         <v>1217</v>
@@ -39370,7 +39552,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="C449">
         <v>1100</v>
@@ -39453,7 +39635,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>450</v>
+        <v>476</v>
       </c>
       <c r="C450">
         <v>1058</v>
@@ -39536,7 +39718,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="C451">
         <v>1019</v>
@@ -39619,7 +39801,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>452</v>
+        <v>478</v>
       </c>
       <c r="C452">
         <v>1082</v>
@@ -39702,7 +39884,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="C453">
         <v>987</v>
@@ -39785,7 +39967,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>454</v>
+        <v>480</v>
       </c>
       <c r="C454">
         <v>1109</v>
@@ -39868,7 +40050,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
       <c r="C455">
         <v>1108</v>
@@ -39951,7 +40133,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>456</v>
+        <v>482</v>
       </c>
       <c r="C456">
         <v>897</v>
@@ -40034,7 +40216,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>457</v>
+        <v>483</v>
       </c>
       <c r="C457">
         <v>993</v>
@@ -40117,7 +40299,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="C458">
         <v>1081</v>
@@ -40200,7 +40382,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>459</v>
+        <v>485</v>
       </c>
       <c r="C459">
         <v>1103</v>
@@ -40283,7 +40465,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="C460">
         <v>1127</v>
@@ -40366,7 +40548,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="C461">
         <v>1038</v>
@@ -40449,7 +40631,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="C462">
         <v>1160</v>
@@ -40532,7 +40714,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="C463">
         <v>1117</v>
@@ -40615,7 +40797,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C464">
         <v>613</v>
@@ -40698,7 +40880,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="C465">
         <v>826</v>
@@ -40781,7 +40963,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>466</v>
+        <v>492</v>
       </c>
       <c r="C466">
         <v>1105</v>
@@ -40864,7 +41046,7 @@
         <v>465</v>
       </c>
       <c r="B467" t="s">
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="C467">
         <v>869</v>
@@ -40947,7 +41129,7 @@
         <v>466</v>
       </c>
       <c r="B468" t="s">
-        <v>468</v>
+        <v>494</v>
       </c>
       <c r="C468">
         <v>973</v>
@@ -41030,7 +41212,7 @@
         <v>467</v>
       </c>
       <c r="B469" t="s">
-        <v>469</v>
+        <v>495</v>
       </c>
       <c r="C469">
         <v>886</v>
@@ -41113,7 +41295,7 @@
         <v>468</v>
       </c>
       <c r="B470" t="s">
-        <v>470</v>
+        <v>496</v>
       </c>
       <c r="C470">
         <v>622</v>
@@ -41196,7 +41378,7 @@
         <v>469</v>
       </c>
       <c r="B471" t="s">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="C471">
         <v>972</v>
@@ -41279,7 +41461,7 @@
         <v>470</v>
       </c>
       <c r="B472" t="s">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="C472">
         <v>1030</v>
@@ -41362,7 +41544,7 @@
         <v>471</v>
       </c>
       <c r="B473" t="s">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="C473">
         <v>1000</v>
@@ -41445,7 +41627,7 @@
         <v>472</v>
       </c>
       <c r="B474" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="C474">
         <v>1097</v>
@@ -41528,7 +41710,7 @@
         <v>473</v>
       </c>
       <c r="B475" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="C475">
         <v>1057</v>
@@ -41611,7 +41793,7 @@
         <v>474</v>
       </c>
       <c r="B476" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="C476">
         <v>860</v>
@@ -41694,7 +41876,7 @@
         <v>475</v>
       </c>
       <c r="B477" t="s">
-        <v>477</v>
+        <v>503</v>
       </c>
       <c r="C477">
         <v>1122</v>
@@ -41777,7 +41959,7 @@
         <v>476</v>
       </c>
       <c r="B478" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="C478">
         <v>1050</v>
@@ -41860,7 +42042,7 @@
         <v>477</v>
       </c>
       <c r="B479" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="C479">
         <v>1093</v>
@@ -41943,7 +42125,7 @@
         <v>478</v>
       </c>
       <c r="B480" t="s">
-        <v>480</v>
+        <v>506</v>
       </c>
       <c r="C480">
         <v>1192</v>
@@ -42026,7 +42208,7 @@
         <v>479</v>
       </c>
       <c r="B481" t="s">
-        <v>481</v>
+        <v>507</v>
       </c>
       <c r="C481">
         <v>1066</v>
@@ -42109,7 +42291,7 @@
         <v>480</v>
       </c>
       <c r="B482" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C482">
         <v>1060</v>
@@ -42192,7 +42374,7 @@
         <v>481</v>
       </c>
       <c r="B483" t="s">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="C483">
         <v>1063</v>
@@ -42275,7 +42457,7 @@
         <v>482</v>
       </c>
       <c r="B484" t="s">
-        <v>484</v>
+        <v>510</v>
       </c>
       <c r="C484">
         <v>810</v>
@@ -42358,7 +42540,7 @@
         <v>483</v>
       </c>
       <c r="B485" t="s">
-        <v>485</v>
+        <v>511</v>
       </c>
       <c r="C485">
         <v>843</v>
@@ -42441,7 +42623,7 @@
         <v>484</v>
       </c>
       <c r="B486" t="s">
-        <v>486</v>
+        <v>512</v>
       </c>
       <c r="C486">
         <v>768</v>
@@ -42524,7 +42706,7 @@
         <v>485</v>
       </c>
       <c r="B487" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="C487">
         <v>1049</v>
@@ -42607,7 +42789,7 @@
         <v>486</v>
       </c>
       <c r="B488" t="s">
-        <v>487</v>
+        <v>513</v>
       </c>
       <c r="C488">
         <v>1002</v>
@@ -42690,7 +42872,7 @@
         <v>487</v>
       </c>
       <c r="B489" t="s">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="C489">
         <v>976</v>
@@ -42773,7 +42955,7 @@
         <v>488</v>
       </c>
       <c r="B490" t="s">
-        <v>489</v>
+        <v>515</v>
       </c>
       <c r="C490">
         <v>936</v>
@@ -42856,7 +43038,7 @@
         <v>489</v>
       </c>
       <c r="B491" t="s">
-        <v>490</v>
+        <v>516</v>
       </c>
       <c r="C491">
         <v>868</v>
@@ -42939,7 +43121,7 @@
         <v>490</v>
       </c>
       <c r="B492" t="s">
-        <v>491</v>
+        <v>517</v>
       </c>
       <c r="C492">
         <v>1116</v>
@@ -43022,7 +43204,7 @@
         <v>491</v>
       </c>
       <c r="B493" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="C493">
         <v>946</v>
@@ -43105,7 +43287,7 @@
         <v>492</v>
       </c>
       <c r="B494" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="C494">
         <v>829</v>
@@ -43188,7 +43370,7 @@
         <v>493</v>
       </c>
       <c r="B495" t="s">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="C495">
         <v>1142</v>
@@ -43271,7 +43453,7 @@
         <v>494</v>
       </c>
       <c r="B496" t="s">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="C496">
         <v>1064</v>
@@ -43354,7 +43536,7 @@
         <v>495</v>
       </c>
       <c r="B497" t="s">
-        <v>496</v>
+        <v>522</v>
       </c>
       <c r="C497">
         <v>1063</v>
@@ -43437,7 +43619,7 @@
         <v>496</v>
       </c>
       <c r="B498" t="s">
-        <v>497</v>
+        <v>523</v>
       </c>
       <c r="C498">
         <v>1079</v>
@@ -43520,7 +43702,7 @@
         <v>497</v>
       </c>
       <c r="B499" t="s">
-        <v>498</v>
+        <v>524</v>
       </c>
       <c r="C499">
         <v>1027</v>
@@ -43603,7 +43785,7 @@
         <v>498</v>
       </c>
       <c r="B500" t="s">
-        <v>499</v>
+        <v>525</v>
       </c>
       <c r="C500">
         <v>998</v>
@@ -43686,7 +43868,7 @@
         <v>499</v>
       </c>
       <c r="B501" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="C501">
         <v>1110</v>
@@ -43769,7 +43951,7 @@
         <v>500</v>
       </c>
       <c r="B502" t="s">
-        <v>501</v>
+        <v>527</v>
       </c>
       <c r="C502">
         <v>992</v>
@@ -43852,7 +44034,7 @@
         <v>501</v>
       </c>
       <c r="B503" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="C503">
         <v>947</v>
@@ -43935,7 +44117,7 @@
         <v>502</v>
       </c>
       <c r="B504" t="s">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="C504">
         <v>1095</v>
@@ -44018,7 +44200,7 @@
         <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>504</v>
+        <v>530</v>
       </c>
       <c r="C505">
         <v>1083</v>
@@ -44101,7 +44283,7 @@
         <v>504</v>
       </c>
       <c r="B506" t="s">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="C506">
         <v>1010</v>
@@ -44184,7 +44366,7 @@
         <v>505</v>
       </c>
       <c r="B507" t="s">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="C507">
         <v>1037</v>
@@ -44267,7 +44449,7 @@
         <v>506</v>
       </c>
       <c r="B508" t="s">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="C508">
         <v>1069</v>
@@ -44350,7 +44532,7 @@
         <v>507</v>
       </c>
       <c r="B509" t="s">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="C509">
         <v>1057</v>
@@ -44433,7 +44615,7 @@
         <v>508</v>
       </c>
       <c r="B510" t="s">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="C510">
         <v>1057</v>
@@ -44516,7 +44698,7 @@
         <v>509</v>
       </c>
       <c r="B511" t="s">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="C511">
         <v>1093</v>
@@ -44599,7 +44781,7 @@
         <v>510</v>
       </c>
       <c r="B512" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="C512">
         <v>1065</v>
@@ -44682,7 +44864,7 @@
         <v>511</v>
       </c>
       <c r="B513" t="s">
-        <v>512</v>
+        <v>538</v>
       </c>
       <c r="C513">
         <v>1058</v>
@@ -44765,7 +44947,7 @@
         <v>512</v>
       </c>
       <c r="B514" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="C514">
         <v>1091</v>
@@ -44848,7 +45030,7 @@
         <v>513</v>
       </c>
       <c r="B515" t="s">
-        <v>514</v>
+        <v>540</v>
       </c>
       <c r="C515">
         <v>913</v>
@@ -44931,7 +45113,7 @@
         <v>514</v>
       </c>
       <c r="B516" t="s">
-        <v>515</v>
+        <v>541</v>
       </c>
       <c r="C516">
         <v>1053</v>
@@ -45014,7 +45196,7 @@
         <v>515</v>
       </c>
       <c r="B517" t="s">
-        <v>516</v>
+        <v>542</v>
       </c>
       <c r="C517">
         <v>1093</v>
@@ -45097,7 +45279,7 @@
         <v>516</v>
       </c>
       <c r="B518" t="s">
-        <v>517</v>
+        <v>543</v>
       </c>
       <c r="C518">
         <v>1114</v>
@@ -45180,7 +45362,7 @@
         <v>517</v>
       </c>
       <c r="B519" t="s">
-        <v>518</v>
+        <v>544</v>
       </c>
       <c r="C519">
         <v>1102</v>
@@ -45263,7 +45445,7 @@
         <v>518</v>
       </c>
       <c r="B520" t="s">
-        <v>519</v>
+        <v>545</v>
       </c>
       <c r="C520">
         <v>1103</v>
@@ -45346,7 +45528,7 @@
         <v>519</v>
       </c>
       <c r="B521" t="s">
-        <v>520</v>
+        <v>546</v>
       </c>
       <c r="C521">
         <v>1055</v>
@@ -45429,7 +45611,7 @@
         <v>520</v>
       </c>
       <c r="B522" t="s">
-        <v>521</v>
+        <v>547</v>
       </c>
       <c r="C522">
         <v>1121</v>
@@ -45512,7 +45694,7 @@
         <v>521</v>
       </c>
       <c r="B523" t="s">
-        <v>522</v>
+        <v>548</v>
       </c>
       <c r="C523">
         <v>1166</v>
@@ -45595,7 +45777,7 @@
         <v>522</v>
       </c>
       <c r="B524" t="s">
-        <v>523</v>
+        <v>549</v>
       </c>
       <c r="C524">
         <v>940</v>
@@ -45678,7 +45860,7 @@
         <v>523</v>
       </c>
       <c r="B525" t="s">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="C525">
         <v>1117</v>
@@ -45761,7 +45943,7 @@
         <v>524</v>
       </c>
       <c r="B526" t="s">
-        <v>525</v>
+        <v>551</v>
       </c>
       <c r="C526">
         <v>1018</v>
@@ -45844,7 +46026,7 @@
         <v>525</v>
       </c>
       <c r="B527" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
       <c r="C527">
         <v>1159</v>
@@ -45927,7 +46109,7 @@
         <v>526</v>
       </c>
       <c r="B528" t="s">
-        <v>527</v>
+        <v>553</v>
       </c>
       <c r="C528">
         <v>1175</v>
@@ -46010,7 +46192,7 @@
         <v>527</v>
       </c>
       <c r="B529" t="s">
-        <v>528</v>
+        <v>554</v>
       </c>
       <c r="C529">
         <v>1090</v>
@@ -46093,7 +46275,7 @@
         <v>528</v>
       </c>
       <c r="B530" t="s">
-        <v>529</v>
+        <v>555</v>
       </c>
       <c r="C530">
         <v>990</v>
@@ -46176,7 +46358,7 @@
         <v>529</v>
       </c>
       <c r="B531" t="s">
-        <v>530</v>
+        <v>556</v>
       </c>
       <c r="C531">
         <v>789</v>
@@ -46259,7 +46441,7 @@
         <v>530</v>
       </c>
       <c r="B532" t="s">
-        <v>531</v>
+        <v>557</v>
       </c>
       <c r="C532">
         <v>872</v>
@@ -46342,7 +46524,7 @@
         <v>531</v>
       </c>
       <c r="B533" t="s">
-        <v>532</v>
+        <v>558</v>
       </c>
       <c r="C533">
         <v>677</v>
@@ -46425,7 +46607,7 @@
         <v>532</v>
       </c>
       <c r="B534" t="s">
-        <v>533</v>
+        <v>559</v>
       </c>
       <c r="C534">
         <v>1057</v>
@@ -46508,7 +46690,7 @@
         <v>533</v>
       </c>
       <c r="B535" t="s">
-        <v>534</v>
+        <v>560</v>
       </c>
       <c r="C535">
         <v>1004</v>
@@ -46591,7 +46773,7 @@
         <v>534</v>
       </c>
       <c r="B536" t="s">
-        <v>535</v>
+        <v>561</v>
       </c>
       <c r="C536">
         <v>986</v>
@@ -46674,7 +46856,7 @@
         <v>535</v>
       </c>
       <c r="B537" t="s">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C537">
         <v>1085</v>
@@ -46757,7 +46939,7 @@
         <v>536</v>
       </c>
       <c r="B538" t="s">
-        <v>537</v>
+        <v>563</v>
       </c>
       <c r="C538">
         <v>987</v>
@@ -46840,7 +47022,7 @@
         <v>537</v>
       </c>
       <c r="B539" t="s">
-        <v>538</v>
+        <v>564</v>
       </c>
       <c r="C539">
         <v>977</v>
@@ -46923,7 +47105,7 @@
         <v>538</v>
       </c>
       <c r="B540" t="s">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="C540">
         <v>556</v>
@@ -47006,7 +47188,7 @@
         <v>539</v>
       </c>
       <c r="B541" t="s">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="C541">
         <v>1106</v>
@@ -47089,7 +47271,7 @@
         <v>540</v>
       </c>
       <c r="B542" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="C542">
         <v>1107</v>
@@ -47172,7 +47354,7 @@
         <v>541</v>
       </c>
       <c r="B543" t="s">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C543">
         <v>948</v>
@@ -47255,7 +47437,7 @@
         <v>542</v>
       </c>
       <c r="B544" t="s">
-        <v>543</v>
+        <v>569</v>
       </c>
       <c r="C544">
         <v>852</v>
@@ -47338,7 +47520,7 @@
         <v>543</v>
       </c>
       <c r="B545" t="s">
-        <v>544</v>
+        <v>570</v>
       </c>
       <c r="C545">
         <v>1008</v>
@@ -47421,7 +47603,7 @@
         <v>544</v>
       </c>
       <c r="B546" t="s">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="C546">
         <v>1029</v>
@@ -47504,7 +47686,7 @@
         <v>545</v>
       </c>
       <c r="B547" t="s">
-        <v>546</v>
+        <v>572</v>
       </c>
       <c r="C547">
         <v>970</v>
@@ -47587,7 +47769,7 @@
         <v>546</v>
       </c>
       <c r="B548" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="C548">
         <v>778</v>
@@ -47670,7 +47852,7 @@
         <v>547</v>
       </c>
       <c r="B549" t="s">
-        <v>548</v>
+        <v>574</v>
       </c>
       <c r="C549">
         <v>964</v>
@@ -47753,7 +47935,7 @@
         <v>548</v>
       </c>
       <c r="B550" t="s">
-        <v>549</v>
+        <v>575</v>
       </c>
       <c r="C550">
         <v>979</v>
@@ -47836,7 +48018,7 @@
         <v>549</v>
       </c>
       <c r="B551" t="s">
-        <v>550</v>
+        <v>576</v>
       </c>
       <c r="C551">
         <v>1004</v>
@@ -47919,7 +48101,7 @@
         <v>550</v>
       </c>
       <c r="B552" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="C552">
         <v>673</v>
@@ -48002,7 +48184,7 @@
         <v>551</v>
       </c>
       <c r="B553" t="s">
-        <v>552</v>
+        <v>578</v>
       </c>
       <c r="C553">
         <v>755</v>
@@ -48085,7 +48267,7 @@
         <v>552</v>
       </c>
       <c r="B554" t="s">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="C554">
         <v>721</v>
@@ -48168,7 +48350,7 @@
         <v>553</v>
       </c>
       <c r="B555" t="s">
-        <v>554</v>
+        <v>580</v>
       </c>
       <c r="C555">
         <v>1028</v>
@@ -48251,7 +48433,7 @@
         <v>554</v>
       </c>
       <c r="B556" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="C556">
         <v>1047</v>
@@ -48334,7 +48516,7 @@
         <v>555</v>
       </c>
       <c r="B557" t="s">
-        <v>556</v>
+        <v>582</v>
       </c>
       <c r="C557">
         <v>908</v>
@@ -48417,7 +48599,7 @@
         <v>556</v>
       </c>
       <c r="B558" t="s">
-        <v>557</v>
+        <v>583</v>
       </c>
       <c r="C558">
         <v>905</v>
@@ -48500,7 +48682,7 @@
         <v>557</v>
       </c>
       <c r="B559" t="s">
-        <v>558</v>
+        <v>584</v>
       </c>
       <c r="C559">
         <v>710</v>
@@ -48583,7 +48765,7 @@
         <v>558</v>
       </c>
       <c r="B560" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="C560">
         <v>654</v>
@@ -48666,7 +48848,7 @@
         <v>559</v>
       </c>
       <c r="B561" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="C561">
         <v>804</v>
@@ -48749,7 +48931,7 @@
         <v>560</v>
       </c>
       <c r="B562" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="C562">
         <v>758</v>
@@ -48832,7 +49014,7 @@
         <v>561</v>
       </c>
       <c r="B563" t="s">
-        <v>562</v>
+        <v>588</v>
       </c>
       <c r="C563">
         <v>829</v>
@@ -48915,7 +49097,7 @@
         <v>562</v>
       </c>
       <c r="B564" t="s">
-        <v>563</v>
+        <v>589</v>
       </c>
       <c r="C564">
         <v>901</v>
@@ -48998,7 +49180,7 @@
         <v>563</v>
       </c>
       <c r="B565" t="s">
-        <v>564</v>
+        <v>590</v>
       </c>
       <c r="C565">
         <v>881</v>
@@ -49081,7 +49263,7 @@
         <v>564</v>
       </c>
       <c r="B566" t="s">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="C566">
         <v>1140</v>
@@ -49164,7 +49346,7 @@
         <v>565</v>
       </c>
       <c r="B567" t="s">
-        <v>566</v>
+        <v>592</v>
       </c>
       <c r="C567">
         <v>1141</v>
@@ -49247,7 +49429,7 @@
         <v>566</v>
       </c>
       <c r="B568" t="s">
-        <v>567</v>
+        <v>593</v>
       </c>
       <c r="C568">
         <v>690</v>
@@ -49330,7 +49512,7 @@
         <v>567</v>
       </c>
       <c r="B569" t="s">
-        <v>568</v>
+        <v>594</v>
       </c>
       <c r="C569">
         <v>1197</v>
@@ -49413,7 +49595,7 @@
         <v>568</v>
       </c>
       <c r="B570" t="s">
-        <v>569</v>
+        <v>595</v>
       </c>
       <c r="C570">
         <v>1049</v>
@@ -49496,7 +49678,7 @@
         <v>569</v>
       </c>
       <c r="B571" t="s">
-        <v>570</v>
+        <v>596</v>
       </c>
       <c r="C571">
         <v>1098</v>
@@ -49579,7 +49761,7 @@
         <v>570</v>
       </c>
       <c r="B572" t="s">
-        <v>571</v>
+        <v>597</v>
       </c>
       <c r="C572">
         <v>1164</v>
@@ -49662,7 +49844,7 @@
         <v>571</v>
       </c>
       <c r="B573" t="s">
-        <v>572</v>
+        <v>598</v>
       </c>
       <c r="C573">
         <v>1047</v>
@@ -49745,7 +49927,7 @@
         <v>572</v>
       </c>
       <c r="B574" t="s">
-        <v>573</v>
+        <v>599</v>
       </c>
       <c r="C574">
         <v>815</v>
@@ -49828,7 +50010,7 @@
         <v>573</v>
       </c>
       <c r="B575" t="s">
-        <v>574</v>
+        <v>600</v>
       </c>
       <c r="C575">
         <v>645</v>
@@ -49911,7 +50093,7 @@
         <v>574</v>
       </c>
       <c r="B576" t="s">
-        <v>575</v>
+        <v>601</v>
       </c>
       <c r="C576">
         <v>1127</v>
@@ -49994,7 +50176,7 @@
         <v>575</v>
       </c>
       <c r="B577" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="C577">
         <v>1209</v>
@@ -50077,7 +50259,7 @@
         <v>576</v>
       </c>
       <c r="B578" t="s">
-        <v>577</v>
+        <v>603</v>
       </c>
       <c r="C578">
         <v>740</v>
@@ -50160,7 +50342,7 @@
         <v>577</v>
       </c>
       <c r="B579" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="C579">
         <v>958</v>
@@ -50243,7 +50425,7 @@
         <v>578</v>
       </c>
       <c r="B580" t="s">
-        <v>579</v>
+        <v>605</v>
       </c>
       <c r="C580">
         <v>823</v>
@@ -50326,7 +50508,7 @@
         <v>579</v>
       </c>
       <c r="B581" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="C581">
         <v>791</v>
@@ -50409,7 +50591,7 @@
         <v>580</v>
       </c>
       <c r="B582" t="s">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="C582">
         <v>1151</v>
@@ -50492,7 +50674,7 @@
         <v>581</v>
       </c>
       <c r="B583" t="s">
-        <v>582</v>
+        <v>608</v>
       </c>
       <c r="C583">
         <v>860</v>
@@ -50575,7 +50757,7 @@
         <v>582</v>
       </c>
       <c r="B584" t="s">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="C584">
         <v>1164</v>
@@ -50658,7 +50840,7 @@
         <v>583</v>
       </c>
       <c r="B585" t="s">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="C585">
         <v>1077</v>
@@ -50741,7 +50923,7 @@
         <v>584</v>
       </c>
       <c r="B586" t="s">
-        <v>585</v>
+        <v>611</v>
       </c>
       <c r="C586">
         <v>1131</v>
@@ -50824,7 +51006,7 @@
         <v>585</v>
       </c>
       <c r="B587" t="s">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="C587">
         <v>874</v>
@@ -50907,7 +51089,7 @@
         <v>586</v>
       </c>
       <c r="B588" t="s">
-        <v>587</v>
+        <v>613</v>
       </c>
       <c r="C588">
         <v>609</v>
@@ -50990,7 +51172,7 @@
         <v>587</v>
       </c>
       <c r="B589" t="s">
-        <v>588</v>
+        <v>614</v>
       </c>
       <c r="C589">
         <v>1060</v>
@@ -51073,7 +51255,7 @@
         <v>588</v>
       </c>
       <c r="B590" t="s">
-        <v>589</v>
+        <v>615</v>
       </c>
       <c r="C590">
         <v>1035</v>
@@ -51156,7 +51338,7 @@
         <v>589</v>
       </c>
       <c r="B591" t="s">
-        <v>590</v>
+        <v>616</v>
       </c>
       <c r="C591">
         <v>1014</v>
@@ -51239,7 +51421,7 @@
         <v>590</v>
       </c>
       <c r="B592" t="s">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="C592">
         <v>979</v>
@@ -51322,7 +51504,7 @@
         <v>591</v>
       </c>
       <c r="B593" t="s">
-        <v>592</v>
+        <v>618</v>
       </c>
       <c r="C593">
         <v>1073</v>
@@ -51405,7 +51587,7 @@
         <v>592</v>
       </c>
       <c r="B594" t="s">
-        <v>593</v>
+        <v>619</v>
       </c>
       <c r="C594">
         <v>867</v>
@@ -51488,7 +51670,7 @@
         <v>593</v>
       </c>
       <c r="B595" t="s">
-        <v>594</v>
+        <v>620</v>
       </c>
       <c r="C595">
         <v>844</v>
@@ -51571,7 +51753,7 @@
         <v>594</v>
       </c>
       <c r="B596" t="s">
-        <v>595</v>
+        <v>621</v>
       </c>
       <c r="C596">
         <v>990</v>
@@ -51654,7 +51836,7 @@
         <v>595</v>
       </c>
       <c r="B597" t="s">
-        <v>596</v>
+        <v>622</v>
       </c>
       <c r="C597">
         <v>956</v>
@@ -51737,7 +51919,7 @@
         <v>596</v>
       </c>
       <c r="B598" t="s">
-        <v>597</v>
+        <v>623</v>
       </c>
       <c r="C598">
         <v>651</v>
@@ -51820,7 +52002,7 @@
         <v>597</v>
       </c>
       <c r="B599" t="s">
-        <v>598</v>
+        <v>624</v>
       </c>
       <c r="C599">
         <v>693</v>
@@ -51903,7 +52085,7 @@
         <v>598</v>
       </c>
       <c r="B600" t="s">
-        <v>599</v>
+        <v>625</v>
       </c>
       <c r="C600">
         <v>628</v>
@@ -51986,7 +52168,7 @@
         <v>599</v>
       </c>
       <c r="B601" t="s">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="C601">
         <v>894</v>
@@ -52069,7 +52251,7 @@
         <v>600</v>
       </c>
       <c r="B602" t="s">
-        <v>601</v>
+        <v>627</v>
       </c>
       <c r="C602">
         <v>845</v>
@@ -52152,7 +52334,7 @@
         <v>601</v>
       </c>
       <c r="B603" t="s">
-        <v>602</v>
+        <v>628</v>
       </c>
       <c r="C603">
         <v>891</v>
@@ -52235,7 +52417,7 @@
         <v>602</v>
       </c>
       <c r="B604" t="s">
-        <v>603</v>
+        <v>629</v>
       </c>
       <c r="C604">
         <v>939</v>
@@ -52318,7 +52500,7 @@
         <v>603</v>
       </c>
       <c r="B605" t="s">
-        <v>604</v>
+        <v>630</v>
       </c>
       <c r="C605">
         <v>599</v>
@@ -52401,7 +52583,7 @@
         <v>604</v>
       </c>
       <c r="B606" t="s">
-        <v>605</v>
+        <v>631</v>
       </c>
       <c r="C606">
         <v>1123</v>
@@ -52484,7 +52666,7 @@
         <v>605</v>
       </c>
       <c r="B607" t="s">
-        <v>606</v>
+        <v>632</v>
       </c>
       <c r="C607">
         <v>933</v>
@@ -52567,7 +52749,7 @@
         <v>606</v>
       </c>
       <c r="B608" t="s">
-        <v>607</v>
+        <v>633</v>
       </c>
       <c r="C608">
         <v>907</v>
@@ -52650,7 +52832,7 @@
         <v>607</v>
       </c>
       <c r="B609" t="s">
-        <v>608</v>
+        <v>634</v>
       </c>
       <c r="C609">
         <v>1003</v>
@@ -52733,7 +52915,7 @@
         <v>608</v>
       </c>
       <c r="B610" t="s">
-        <v>609</v>
+        <v>635</v>
       </c>
       <c r="C610">
         <v>658</v>
@@ -52816,7 +52998,7 @@
         <v>609</v>
       </c>
       <c r="B611" t="s">
-        <v>610</v>
+        <v>636</v>
       </c>
       <c r="C611">
         <v>628</v>
@@ -52899,7 +53081,7 @@
         <v>610</v>
       </c>
       <c r="B612" t="s">
-        <v>611</v>
+        <v>637</v>
       </c>
       <c r="C612">
         <v>510</v>
